--- a/Data/TestingFile/匯入格式_訂單交期變更_20260728001.xlsx
+++ b/Data/TestingFile/匯入格式_訂單交期變更_20260728001.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ImportDataToERP\Data\TestingFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12925C2C-3B4E-4AD8-9F05-BDC7135FF351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480E7B13-23EB-4262-A001-DD660296338E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="574" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,8 +174,9 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Cascadia Code"/>
-      <family val="3"/>
+      <name val="Noto Sans TC"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="4">
@@ -639,12 +640,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.35">
       <c r="AS3" s="6">
         <v>220</v>
       </c>
       <c r="AT3" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU3" s="7" t="s">
         <v>4</v>
@@ -653,12 +654,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.35">
       <c r="AS4" s="6">
         <v>220</v>
       </c>
       <c r="AT4" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU4" s="7" t="s">
         <v>6</v>
@@ -667,12 +668,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:48" x14ac:dyDescent="0.35">
       <c r="AS5" s="6">
         <v>220</v>
       </c>
       <c r="AT5" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU5" s="7" t="s">
         <v>7</v>
@@ -681,12 +682,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:48" x14ac:dyDescent="0.35">
       <c r="AS6" s="6">
         <v>220</v>
       </c>
       <c r="AT6" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU6" s="7" t="s">
         <v>8</v>
@@ -695,12 +696,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:48" x14ac:dyDescent="0.35">
       <c r="AS7" s="6">
         <v>220</v>
       </c>
       <c r="AT7" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU7" s="7" t="s">
         <v>9</v>
@@ -709,12 +710,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:48" x14ac:dyDescent="0.35">
       <c r="AS8" s="6">
         <v>220</v>
       </c>
       <c r="AT8" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU8" s="7" t="s">
         <v>10</v>
@@ -723,12 +724,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:48" x14ac:dyDescent="0.35">
       <c r="AS9" s="6">
         <v>220</v>
       </c>
       <c r="AT9" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU9" s="7" t="s">
         <v>11</v>
@@ -737,12 +738,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:48" x14ac:dyDescent="0.35">
       <c r="AS10" s="6">
         <v>220</v>
       </c>
       <c r="AT10" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU10" s="7" t="s">
         <v>12</v>
@@ -751,12 +752,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:48" x14ac:dyDescent="0.35">
       <c r="AS11" s="6">
         <v>220</v>
       </c>
       <c r="AT11" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU11" s="7" t="s">
         <v>13</v>
@@ -765,12 +766,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:48" x14ac:dyDescent="0.35">
       <c r="AS12" s="6">
         <v>220</v>
       </c>
       <c r="AT12" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU12" s="7" t="s">
         <v>14</v>
@@ -779,12 +780,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="13" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:48" x14ac:dyDescent="0.35">
       <c r="AS13" s="6">
         <v>220</v>
       </c>
       <c r="AT13" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU13" s="7" t="s">
         <v>15</v>
@@ -793,12 +794,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:48" x14ac:dyDescent="0.35">
       <c r="AS14" s="6">
         <v>220</v>
       </c>
       <c r="AT14" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU14" s="7" t="s">
         <v>16</v>
@@ -807,12 +808,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:48" x14ac:dyDescent="0.35">
       <c r="AS15" s="6">
         <v>220</v>
       </c>
       <c r="AT15" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU15" s="7" t="s">
         <v>17</v>
@@ -821,12 +822,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:48" x14ac:dyDescent="0.35">
       <c r="AS16" s="6">
         <v>220</v>
       </c>
       <c r="AT16" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU16" s="7" t="s">
         <v>18</v>
@@ -835,12 +836,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="17" spans="45:48" x14ac:dyDescent="0.25">
+    <row r="17" spans="45:48" x14ac:dyDescent="0.35">
       <c r="AS17" s="6">
         <v>220</v>
       </c>
       <c r="AT17" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU17" s="7" t="s">
         <v>19</v>
@@ -849,12 +850,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="18" spans="45:48" x14ac:dyDescent="0.25">
+    <row r="18" spans="45:48" x14ac:dyDescent="0.35">
       <c r="AS18" s="6">
         <v>220</v>
       </c>
       <c r="AT18" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU18" s="7" t="s">
         <v>20</v>
@@ -863,12 +864,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="19" spans="45:48" x14ac:dyDescent="0.25">
+    <row r="19" spans="45:48" x14ac:dyDescent="0.35">
       <c r="AS19" s="6">
         <v>220</v>
       </c>
       <c r="AT19" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU19" s="7" t="s">
         <v>21</v>
@@ -877,12 +878,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="20" spans="45:48" x14ac:dyDescent="0.25">
+    <row r="20" spans="45:48" x14ac:dyDescent="0.35">
       <c r="AS20" s="6">
         <v>220</v>
       </c>
       <c r="AT20" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU20" s="7" t="s">
         <v>22</v>
@@ -891,12 +892,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="21" spans="45:48" x14ac:dyDescent="0.25">
+    <row r="21" spans="45:48" x14ac:dyDescent="0.35">
       <c r="AS21" s="6">
         <v>220</v>
       </c>
       <c r="AT21" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU21" s="7" t="s">
         <v>23</v>
@@ -905,12 +906,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="22" spans="45:48" x14ac:dyDescent="0.25">
+    <row r="22" spans="45:48" x14ac:dyDescent="0.35">
       <c r="AS22" s="6">
         <v>220</v>
       </c>
       <c r="AT22" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU22" s="7" t="s">
         <v>24</v>
@@ -919,12 +920,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="23" spans="45:48" x14ac:dyDescent="0.25">
+    <row r="23" spans="45:48" x14ac:dyDescent="0.35">
       <c r="AS23" s="6">
         <v>220</v>
       </c>
       <c r="AT23" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU23" s="7" t="s">
         <v>25</v>
@@ -933,12 +934,12 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="24" spans="45:48" x14ac:dyDescent="0.25">
+    <row r="24" spans="45:48" x14ac:dyDescent="0.35">
       <c r="AS24" s="6">
         <v>220</v>
       </c>
       <c r="AT24" s="11">
-        <v>20251231019</v>
+        <v>20251231017</v>
       </c>
       <c r="AU24" s="7" t="s">
         <v>26</v>

--- a/Data/TestingFile/匯入格式_訂單交期變更_20260728001.xlsx
+++ b/Data/TestingFile/匯入格式_訂單交期變更_20260728001.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ImportDataToERP\Data\TestingFile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ImportDataToERP\Data\TestingFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480E7B13-23EB-4262-A001-DD660296338E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7316DFE5-123A-4D1F-AAC4-AE41ED9272B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="574" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="574" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="批次匯入表" sheetId="1" r:id="rId1"/>
@@ -173,10 +173,9 @@
       <charset val="136"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Noto Sans TC"/>
-      <family val="2"/>
-      <charset val="136"/>
+      <sz val="7"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="4">
@@ -248,9 +247,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="一般 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="一般 5" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -266,7 +265,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -564,18 +563,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="工作表1"/>
   <dimension ref="A1:AV24"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="4"/>
+    <col min="1" max="1" width="9.1796875" style="4"/>
     <col min="2" max="44" width="0" style="5" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="8.77734375" style="5" customWidth="1"/>
-    <col min="46" max="46" width="13.109375" style="5" customWidth="1"/>
-    <col min="47" max="47" width="8.77734375" style="5" customWidth="1"/>
-    <col min="48" max="48" width="9.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="49" max="16384" width="9.21875" style="5"/>
+    <col min="45" max="45" width="8.81640625" style="5" customWidth="1"/>
+    <col min="46" max="46" width="13.08984375" style="5" customWidth="1"/>
+    <col min="47" max="47" width="8.81640625" style="5" customWidth="1"/>
+    <col min="48" max="48" width="9.90625" style="5" bestFit="1" customWidth="1"/>
+    <col min="49" max="16384" width="9.1796875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="3" customFormat="1" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" s="3" customFormat="1" ht="39" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -626,7 +625,7 @@
       <c r="AT1" s="2"/>
       <c r="AU1" s="2"/>
     </row>
-    <row r="2" spans="1:48" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:48" ht="13.5" x14ac:dyDescent="0.25">
       <c r="AS2" s="9" t="s">
         <v>2</v>
       </c>
@@ -640,7 +639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AS3" s="6">
         <v>220</v>
       </c>
@@ -654,7 +653,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AS4" s="6">
         <v>220</v>
       </c>
@@ -668,7 +667,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AS5" s="6">
         <v>220</v>
       </c>
@@ -682,7 +681,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AS6" s="6">
         <v>220</v>
       </c>
@@ -696,7 +695,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AS7" s="6">
         <v>220</v>
       </c>
@@ -710,7 +709,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AS8" s="6">
         <v>220</v>
       </c>
@@ -724,7 +723,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AS9" s="6">
         <v>220</v>
       </c>
@@ -738,7 +737,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AS10" s="6">
         <v>220</v>
       </c>
@@ -752,7 +751,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AS11" s="6">
         <v>220</v>
       </c>
@@ -766,7 +765,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AS12" s="6">
         <v>220</v>
       </c>
@@ -780,7 +779,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="13" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AS13" s="6">
         <v>220</v>
       </c>
@@ -794,7 +793,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AS14" s="6">
         <v>220</v>
       </c>
@@ -808,7 +807,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AS15" s="6">
         <v>220</v>
       </c>
@@ -822,7 +821,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AS16" s="6">
         <v>220</v>
       </c>
@@ -836,7 +835,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="17" spans="45:48" x14ac:dyDescent="0.35">
+    <row r="17" spans="45:48" x14ac:dyDescent="0.25">
       <c r="AS17" s="6">
         <v>220</v>
       </c>
@@ -850,7 +849,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="18" spans="45:48" x14ac:dyDescent="0.35">
+    <row r="18" spans="45:48" x14ac:dyDescent="0.25">
       <c r="AS18" s="6">
         <v>220</v>
       </c>
@@ -864,7 +863,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="19" spans="45:48" x14ac:dyDescent="0.35">
+    <row r="19" spans="45:48" x14ac:dyDescent="0.25">
       <c r="AS19" s="6">
         <v>220</v>
       </c>
@@ -878,7 +877,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="20" spans="45:48" x14ac:dyDescent="0.35">
+    <row r="20" spans="45:48" x14ac:dyDescent="0.25">
       <c r="AS20" s="6">
         <v>220</v>
       </c>
@@ -892,7 +891,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="21" spans="45:48" x14ac:dyDescent="0.35">
+    <row r="21" spans="45:48" x14ac:dyDescent="0.25">
       <c r="AS21" s="6">
         <v>220</v>
       </c>
@@ -906,7 +905,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="22" spans="45:48" x14ac:dyDescent="0.35">
+    <row r="22" spans="45:48" x14ac:dyDescent="0.25">
       <c r="AS22" s="6">
         <v>220</v>
       </c>
@@ -920,7 +919,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="23" spans="45:48" x14ac:dyDescent="0.35">
+    <row r="23" spans="45:48" x14ac:dyDescent="0.25">
       <c r="AS23" s="6">
         <v>220</v>
       </c>
@@ -934,7 +933,7 @@
         <v>20260728</v>
       </c>
     </row>
-    <row r="24" spans="45:48" x14ac:dyDescent="0.35">
+    <row r="24" spans="45:48" x14ac:dyDescent="0.25">
       <c r="AS24" s="6">
         <v>220</v>
       </c>
